--- a/documents/ALP_blast.xlsx
+++ b/documents/ALP_blast.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ALP neighbors" sheetId="3" r:id="rId1"/>
     <sheet name="ALP types" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1915,7 +1915,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2019,6 +2019,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Liberation Sans"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -2269,7 +2274,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2308,6 +2313,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent" xfId="1"/>
@@ -2404,7 +2410,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="__Anonymous_Sheet_DB__0" displayName="__Anonymous_Sheet_DB__0" ref="A1:K139" totalsRowShown="0">
   <sortState ref="A2:K139">
-    <sortCondition ref="K24"/>
+    <sortCondition ref="K37"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" name="i"/>
@@ -5176,8 +5182,8 @@
     <col min="6" max="6" width="17.8984375" customWidth="1"/>
     <col min="7" max="7" width="22.19921875" customWidth="1"/>
     <col min="8" max="8" width="29.3984375" customWidth="1"/>
-    <col min="9" max="9" width="14.59765625" customWidth="1"/>
-    <col min="10" max="10" width="5" customWidth="1"/>
+    <col min="9" max="9" width="21.796875" customWidth="1"/>
+    <col min="10" max="10" width="5.296875" customWidth="1"/>
     <col min="11" max="11" width="10.59765625" customWidth="1"/>
     <col min="14" max="14" width="21.09765625" customWidth="1"/>
   </cols>
@@ -5220,7 +5226,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="7" t="e">
-        <f t="shared" ref="A2:A33" si="0">A1+1</f>
+        <f>A1+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -5262,7 +5268,7 @@
     </row>
     <row r="3" spans="1:14" ht="14.4">
       <c r="A3" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A2+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5302,7 +5308,7 @@
     </row>
     <row r="4" spans="1:14" ht="14.4">
       <c r="A4" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A3+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -5342,7 +5348,7 @@
     </row>
     <row r="5" spans="1:14" ht="14.4">
       <c r="A5" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A4+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -5382,7 +5388,7 @@
     </row>
     <row r="6" spans="1:14" ht="14.4" thickBot="1">
       <c r="A6" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A5+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -5424,7 +5430,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A6+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -5466,7 +5472,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A7+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5502,7 +5508,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A8+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5538,7 +5544,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A9+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5574,7 +5580,7 @@
     </row>
     <row r="11" spans="1:14" ht="14.4" thickBot="1">
       <c r="A11" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A10+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -5610,7 +5616,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A11+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -5646,7 +5652,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A12+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -5682,7 +5688,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A13+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -5718,7 +5724,7 @@
     </row>
     <row r="15" spans="1:14" ht="14.4" thickBot="1">
       <c r="A15" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A14+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="14" t="s">
@@ -5754,7 +5760,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A15+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -5790,7 +5796,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A16+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -5826,7 +5832,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A17+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -5862,7 +5868,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A18+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -5898,7 +5904,7 @@
     </row>
     <row r="20" spans="1:11" ht="14.4" thickBot="1">
       <c r="A20" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A19+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -5934,7 +5940,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A20+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -5970,7 +5976,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A21+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -6006,7 +6012,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A22+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -6042,7 +6048,7 @@
     </row>
     <row r="24" spans="1:11" ht="14.4" thickBot="1">
       <c r="A24" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A23+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -6078,7 +6084,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A24+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -6114,7 +6120,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A25+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -6150,7 +6156,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A26+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -6186,7 +6192,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A27+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -6222,7 +6228,7 @@
     </row>
     <row r="29" spans="1:11" ht="14.4" thickBot="1">
       <c r="A29" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A28+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B29" s="14" t="s">
@@ -6258,7 +6264,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="7" t="e">
-        <f t="shared" si="0"/>
+        <f>A29+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -6294,7 +6300,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A30+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -6330,7 +6336,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="10" t="e">
-        <f t="shared" si="0"/>
+        <f>A31+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -6366,7 +6372,7 @@
     </row>
     <row r="33" spans="1:11" ht="14.4" thickBot="1">
       <c r="A33" s="13" t="e">
-        <f t="shared" si="0"/>
+        <f>A32+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -6402,7 +6408,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="7" t="e">
-        <f t="shared" ref="A34:A65" si="1">A33+1</f>
+        <f>A33+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -6438,7 +6444,7 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A34+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -6474,7 +6480,7 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A35+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -6510,7 +6516,7 @@
     </row>
     <row r="37" spans="1:11" ht="14.4" thickBot="1">
       <c r="A37" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A36+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -6546,7 +6552,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A37+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -6582,7 +6588,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A38+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6618,7 +6624,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A39+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -6654,7 +6660,7 @@
     </row>
     <row r="41" spans="1:11" ht="14.4" thickBot="1">
       <c r="A41" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A40+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -6690,7 +6696,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A41+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -6726,7 +6732,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A42+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -6762,32 +6768,32 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A43+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D44" s="1">
-        <v>336996</v>
+        <v>58565</v>
       </c>
       <c r="E44" s="1">
-        <v>337826</v>
+        <v>60262</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>337</v>
+        <v>465</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>17</v>
@@ -6798,32 +6804,32 @@
     </row>
     <row r="45" spans="1:11" ht="14.4" thickBot="1">
       <c r="A45" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A44+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="D45" s="14">
-        <v>58565</v>
+        <v>288718</v>
       </c>
       <c r="E45" s="14">
-        <v>60262</v>
+        <v>290439</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="H45" s="14" t="s">
         <v>21</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="J45" s="14" t="s">
         <v>17</v>
@@ -6834,32 +6840,32 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A45+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="D46" s="8">
-        <v>288718</v>
+        <v>176010</v>
       </c>
       <c r="E46" s="8">
-        <v>290439</v>
+        <v>177719</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="J46" s="8" t="s">
         <v>17</v>
@@ -6870,32 +6876,32 @@
     </row>
     <row r="47" spans="1:11" ht="14.4" thickBot="1">
       <c r="A47" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A46+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="D47" s="14">
-        <v>176010</v>
+        <v>419566</v>
       </c>
       <c r="E47" s="14">
-        <v>177719</v>
+        <v>421140</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="J47" s="14" t="s">
         <v>17</v>
@@ -6906,32 +6912,32 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A47+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="D48" s="8">
-        <v>419566</v>
+        <v>395988</v>
       </c>
       <c r="E48" s="8">
-        <v>421140</v>
+        <v>397562</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="J48" s="8" t="s">
         <v>17</v>
@@ -6942,43 +6948,43 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A48+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>529</v>
+        <v>444</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>530</v>
+        <v>448</v>
       </c>
       <c r="D49" s="1">
-        <v>395988</v>
+        <v>336996</v>
       </c>
       <c r="E49" s="1">
-        <v>397562</v>
+        <v>337826</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>531</v>
+        <v>449</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>532</v>
+        <v>450</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>533</v>
+        <v>337</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K49" s="11">
-        <v>0</v>
+      <c r="K49" s="38">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A49+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -7014,7 +7020,7 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A50+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -7050,7 +7056,7 @@
     </row>
     <row r="52" spans="1:11" ht="14.4" thickBot="1">
       <c r="A52" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A51+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -7086,7 +7092,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A52+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -7122,7 +7128,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A53+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -7158,7 +7164,7 @@
     </row>
     <row r="55" spans="1:11" ht="14.4" thickBot="1">
       <c r="A55" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A54+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B55" s="14" t="s">
@@ -7194,7 +7200,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A55+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -7230,7 +7236,7 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A56+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -7266,7 +7272,7 @@
     </row>
     <row r="58" spans="1:11" ht="14.4" thickBot="1">
       <c r="A58" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A57+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B58" s="14" t="s">
@@ -7302,7 +7308,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A58+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -7338,7 +7344,7 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A59+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -7374,7 +7380,7 @@
     </row>
     <row r="61" spans="1:11" ht="14.4" thickBot="1">
       <c r="A61" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A60+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B61" s="14" t="s">
@@ -7410,7 +7416,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A61+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -7446,7 +7452,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="10" t="e">
-        <f t="shared" si="1"/>
+        <f>A62+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -7482,7 +7488,7 @@
     </row>
     <row r="64" spans="1:11" ht="14.4" thickBot="1">
       <c r="A64" s="13" t="e">
-        <f t="shared" si="1"/>
+        <f>A63+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -7518,7 +7524,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="7" t="e">
-        <f t="shared" si="1"/>
+        <f>A64+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -7554,7 +7560,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="10" t="e">
-        <f t="shared" ref="A66:A95" si="2">A65+1</f>
+        <f>A65+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -7590,7 +7596,7 @@
     </row>
     <row r="67" spans="1:11" ht="14.4" thickBot="1">
       <c r="A67" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A66+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -7626,7 +7632,7 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A67+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -7662,7 +7668,7 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A68+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -7698,7 +7704,7 @@
     </row>
     <row r="70" spans="1:11" ht="14.4" thickBot="1">
       <c r="A70" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A69+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B70" s="14" t="s">
@@ -7734,7 +7740,7 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A70+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -7770,7 +7776,7 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A71+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -7806,7 +7812,7 @@
     </row>
     <row r="73" spans="1:11" ht="14.4" thickBot="1">
       <c r="A73" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A72+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B73" s="14" t="s">
@@ -7842,7 +7848,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A73+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -7878,7 +7884,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A74+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -7914,7 +7920,7 @@
     </row>
     <row r="76" spans="1:11" ht="14.4" thickBot="1">
       <c r="A76" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A75+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B76" s="14" t="s">
@@ -7950,7 +7956,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A76+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -7986,7 +7992,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A77+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -8022,7 +8028,7 @@
     </row>
     <row r="79" spans="1:11" ht="14.4" thickBot="1">
       <c r="A79" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A78+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B79" s="14" t="s">
@@ -8058,7 +8064,7 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A79+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -8094,7 +8100,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A80+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -8130,7 +8136,7 @@
     </row>
     <row r="82" spans="1:11" ht="14.4" thickBot="1">
       <c r="A82" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A81+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B82" s="14" t="s">
@@ -8166,7 +8172,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A82+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -8202,7 +8208,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A83+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -8238,7 +8244,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A84+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -8274,7 +8280,7 @@
     </row>
     <row r="86" spans="1:11" ht="14.4" thickBot="1">
       <c r="A86" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A85+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B86" s="14" t="s">
@@ -8310,7 +8316,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A86+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -8346,7 +8352,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A87+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -8382,7 +8388,7 @@
     </row>
     <row r="89" spans="1:11" ht="14.4" thickBot="1">
       <c r="A89" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A88+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B89" s="14" t="s">
@@ -8418,7 +8424,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A89+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -8454,7 +8460,7 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A90+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -8490,7 +8496,7 @@
     </row>
     <row r="92" spans="1:11" ht="14.4" thickBot="1">
       <c r="A92" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A91+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B92" s="14" t="s">
@@ -8526,7 +8532,7 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="7" t="e">
-        <f t="shared" si="2"/>
+        <f>A92+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -8562,7 +8568,7 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="10" t="e">
-        <f t="shared" si="2"/>
+        <f>A93+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -8598,7 +8604,7 @@
     </row>
     <row r="95" spans="1:11" ht="14.4" thickBot="1">
       <c r="A95" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f>A94+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B95" s="14" t="s">
@@ -8669,7 +8675,7 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="10">
-        <f t="shared" ref="A97:A139" si="3">A96+1</f>
+        <f>A96+1</f>
         <v>2</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -8705,7 +8711,7 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="10">
-        <f t="shared" si="3"/>
+        <f>A97+1</f>
         <v>3</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -8741,7 +8747,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="10">
-        <f t="shared" si="3"/>
+        <f>A98+1</f>
         <v>4</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -8777,7 +8783,7 @@
     </row>
     <row r="100" spans="1:11" ht="14.4" thickBot="1">
       <c r="A100" s="13">
-        <f t="shared" si="3"/>
+        <f>A99+1</f>
         <v>5</v>
       </c>
       <c r="B100" s="14" t="s">
@@ -8813,7 +8819,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="7">
-        <f t="shared" si="3"/>
+        <f>A100+1</f>
         <v>6</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -8849,7 +8855,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="10">
-        <f t="shared" si="3"/>
+        <f>A101+1</f>
         <v>7</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -8885,7 +8891,7 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="10">
-        <f t="shared" si="3"/>
+        <f>A102+1</f>
         <v>8</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -8921,7 +8927,7 @@
     </row>
     <row r="104" spans="1:11" ht="14.4" thickBot="1">
       <c r="A104" s="13">
-        <f t="shared" si="3"/>
+        <f>A103+1</f>
         <v>9</v>
       </c>
       <c r="B104" s="14" t="s">
@@ -8957,7 +8963,7 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="7">
-        <f t="shared" si="3"/>
+        <f>A104+1</f>
         <v>10</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -8993,7 +8999,7 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="10">
-        <f t="shared" si="3"/>
+        <f>A105+1</f>
         <v>11</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -9029,7 +9035,7 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="10">
-        <f t="shared" si="3"/>
+        <f>A106+1</f>
         <v>12</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -9065,7 +9071,7 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="10">
-        <f t="shared" si="3"/>
+        <f>A107+1</f>
         <v>13</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -9101,7 +9107,7 @@
     </row>
     <row r="109" spans="1:11" ht="14.4" thickBot="1">
       <c r="A109" s="13">
-        <f t="shared" si="3"/>
+        <f>A108+1</f>
         <v>14</v>
       </c>
       <c r="B109" s="14" t="s">
@@ -9137,7 +9143,7 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="7">
-        <f t="shared" si="3"/>
+        <f>A109+1</f>
         <v>15</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -9173,7 +9179,7 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="10">
-        <f t="shared" si="3"/>
+        <f>A110+1</f>
         <v>16</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -9209,7 +9215,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="10">
-        <f t="shared" si="3"/>
+        <f>A111+1</f>
         <v>17</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -9245,7 +9251,7 @@
     </row>
     <row r="113" spans="1:11" ht="14.4" thickBot="1">
       <c r="A113" s="13">
-        <f t="shared" si="3"/>
+        <f>A112+1</f>
         <v>18</v>
       </c>
       <c r="B113" s="14" t="s">
@@ -9281,7 +9287,7 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="7">
-        <f t="shared" si="3"/>
+        <f>A113+1</f>
         <v>19</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -9317,7 +9323,7 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="10">
-        <f t="shared" si="3"/>
+        <f>A114+1</f>
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -9353,7 +9359,7 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="10">
-        <f t="shared" si="3"/>
+        <f>A115+1</f>
         <v>21</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -9389,7 +9395,7 @@
     </row>
     <row r="117" spans="1:11" ht="14.4" thickBot="1">
       <c r="A117" s="13">
-        <f t="shared" si="3"/>
+        <f>A116+1</f>
         <v>22</v>
       </c>
       <c r="B117" s="14" t="s">
@@ -9425,7 +9431,7 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="7">
-        <f t="shared" si="3"/>
+        <f>A117+1</f>
         <v>23</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -9461,7 +9467,7 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="10">
-        <f t="shared" si="3"/>
+        <f>A118+1</f>
         <v>24</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -9497,7 +9503,7 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="10">
-        <f t="shared" si="3"/>
+        <f>A119+1</f>
         <v>25</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -9533,7 +9539,7 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="10">
-        <f t="shared" si="3"/>
+        <f>A120+1</f>
         <v>26</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -9569,7 +9575,7 @@
     </row>
     <row r="122" spans="1:11" ht="14.4" thickBot="1">
       <c r="A122" s="13">
-        <f t="shared" si="3"/>
+        <f>A121+1</f>
         <v>27</v>
       </c>
       <c r="B122" s="14" t="s">
@@ -9605,7 +9611,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="7">
-        <f t="shared" si="3"/>
+        <f>A122+1</f>
         <v>28</v>
       </c>
       <c r="B123" s="8" t="s">
@@ -9641,7 +9647,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="10">
-        <f t="shared" si="3"/>
+        <f>A123+1</f>
         <v>29</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -9677,7 +9683,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="10">
-        <f t="shared" si="3"/>
+        <f>A124+1</f>
         <v>30</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -9713,7 +9719,7 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="10">
-        <f t="shared" si="3"/>
+        <f>A125+1</f>
         <v>31</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -9749,7 +9755,7 @@
     </row>
     <row r="127" spans="1:11" ht="14.4" thickBot="1">
       <c r="A127" s="13">
-        <f t="shared" si="3"/>
+        <f>A126+1</f>
         <v>32</v>
       </c>
       <c r="B127" s="14" t="s">
@@ -9785,7 +9791,7 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="7">
-        <f t="shared" si="3"/>
+        <f>A127+1</f>
         <v>33</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -9821,7 +9827,7 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="10">
-        <f t="shared" si="3"/>
+        <f>A128+1</f>
         <v>34</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -9857,7 +9863,7 @@
     </row>
     <row r="130" spans="1:11" ht="14.4" thickBot="1">
       <c r="A130" s="13">
-        <f t="shared" si="3"/>
+        <f>A129+1</f>
         <v>35</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -9893,7 +9899,7 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="7">
-        <f t="shared" si="3"/>
+        <f>A130+1</f>
         <v>36</v>
       </c>
       <c r="B131" s="8" t="s">
@@ -9929,7 +9935,7 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="10">
-        <f t="shared" si="3"/>
+        <f>A131+1</f>
         <v>37</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -9965,7 +9971,7 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="10">
-        <f t="shared" si="3"/>
+        <f>A132+1</f>
         <v>38</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -10001,7 +10007,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="10">
-        <f t="shared" si="3"/>
+        <f>A133+1</f>
         <v>39</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -10037,7 +10043,7 @@
     </row>
     <row r="135" spans="1:11" ht="14.4" thickBot="1">
       <c r="A135" s="13">
-        <f t="shared" si="3"/>
+        <f>A134+1</f>
         <v>40</v>
       </c>
       <c r="B135" s="14" t="s">
@@ -10073,7 +10079,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="7">
-        <f t="shared" si="3"/>
+        <f>A135+1</f>
         <v>41</v>
       </c>
       <c r="B136" s="8" t="s">
@@ -10109,7 +10115,7 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="10">
-        <f t="shared" si="3"/>
+        <f>A136+1</f>
         <v>42</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -10145,7 +10151,7 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="10">
-        <f t="shared" si="3"/>
+        <f>A137+1</f>
         <v>43</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -10181,7 +10187,7 @@
     </row>
     <row r="139" spans="1:11" ht="14.4" thickBot="1">
       <c r="A139" s="13">
-        <f t="shared" si="3"/>
+        <f>A138+1</f>
         <v>44</v>
       </c>
       <c r="B139" s="14" t="s">
@@ -10217,7 +10223,7 @@
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>

--- a/documents/ALP_blast.xlsx
+++ b/documents/ALP_blast.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ALP neighbors" sheetId="3" r:id="rId1"/>
     <sheet name="ALP types" sheetId="1" r:id="rId2"/>
+    <sheet name="Alkaline phosphatase" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="627">
   <si>
     <t>i</t>
   </si>
@@ -2336,7 +2337,1147 @@
     <cellStyle name="Warning" xfId="18"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="147">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="45">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="0.5">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color theme="0"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2730,6 +3871,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="49.5" customWidth="1"/>
+    <col min="21" max="21" width="82.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="14.4" thickBot="1">
@@ -5142,27 +6284,27 @@
     <sortCondition ref="A1"/>
   </sortState>
   <conditionalFormatting sqref="A1:U36">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="dcd">
+    <cfRule type="containsText" dxfId="146" priority="7" operator="containsText" text="dcd">
       <formula>NOT(ISERROR(SEARCH("dcd",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:U36">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="alkaline phosphatase">
+    <cfRule type="containsText" dxfId="145" priority="1" operator="containsText" text="alkaline phosphatase">
       <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="rsxA">
+    <cfRule type="containsText" dxfId="144" priority="2" operator="containsText" text="rsxA">
       <formula>NOT(ISERROR(SEARCH("rsxA",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="cell wall hydrolase">
+    <cfRule type="containsText" dxfId="143" priority="3" operator="containsText" text="cell wall hydrolase">
       <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="DUF3465">
+    <cfRule type="containsText" dxfId="142" priority="4" operator="containsText" text="DUF3465">
       <formula>NOT(ISERROR(SEARCH("DUF3465",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="terB">
+    <cfRule type="containsText" dxfId="141" priority="5" operator="containsText" text="terB">
       <formula>NOT(ISERROR(SEARCH("terB",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="metG">
+    <cfRule type="containsText" dxfId="140" priority="6" operator="containsText" text="metG">
       <formula>NOT(ISERROR(SEARCH("metG",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5226,7 +6368,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="7" t="e">
-        <f>A1+1</f>
+        <f t="shared" ref="A2:A33" si="0">A1+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -5268,7 +6410,7 @@
     </row>
     <row r="3" spans="1:14" ht="14.4">
       <c r="A3" s="10" t="e">
-        <f>A2+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -5308,7 +6450,7 @@
     </row>
     <row r="4" spans="1:14" ht="14.4">
       <c r="A4" s="10" t="e">
-        <f>A3+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -5348,7 +6490,7 @@
     </row>
     <row r="5" spans="1:14" ht="14.4">
       <c r="A5" s="10" t="e">
-        <f>A4+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -5388,7 +6530,7 @@
     </row>
     <row r="6" spans="1:14" ht="14.4" thickBot="1">
       <c r="A6" s="13" t="e">
-        <f>A5+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -5430,7 +6572,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="7" t="e">
-        <f>A6+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -5472,7 +6614,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="10" t="e">
-        <f>A7+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -5508,7 +6650,7 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="10" t="e">
-        <f>A8+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -5544,7 +6686,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="10" t="e">
-        <f>A9+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -5580,7 +6722,7 @@
     </row>
     <row r="11" spans="1:14" ht="14.4" thickBot="1">
       <c r="A11" s="13" t="e">
-        <f>A10+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -5616,7 +6758,7 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="7" t="e">
-        <f>A11+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -5652,7 +6794,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="10" t="e">
-        <f>A12+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -5688,7 +6830,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="10" t="e">
-        <f>A13+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -5724,7 +6866,7 @@
     </row>
     <row r="15" spans="1:14" ht="14.4" thickBot="1">
       <c r="A15" s="13" t="e">
-        <f>A14+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B15" s="14" t="s">
@@ -5760,7 +6902,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="7" t="e">
-        <f>A15+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -5796,7 +6938,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="10" t="e">
-        <f>A16+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -5832,7 +6974,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="10" t="e">
-        <f>A17+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -5868,7 +7010,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="10" t="e">
-        <f>A18+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -5904,7 +7046,7 @@
     </row>
     <row r="20" spans="1:11" ht="14.4" thickBot="1">
       <c r="A20" s="13" t="e">
-        <f>A19+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -5940,7 +7082,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="7" t="e">
-        <f>A20+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -5976,7 +7118,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="10" t="e">
-        <f>A21+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -6012,7 +7154,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="10" t="e">
-        <f>A22+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -6048,7 +7190,7 @@
     </row>
     <row r="24" spans="1:11" ht="14.4" thickBot="1">
       <c r="A24" s="13" t="e">
-        <f>A23+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -6084,7 +7226,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="7" t="e">
-        <f>A24+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -6120,7 +7262,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="10" t="e">
-        <f>A25+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -6156,7 +7298,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="10" t="e">
-        <f>A26+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -6192,7 +7334,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="10" t="e">
-        <f>A27+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -6228,7 +7370,7 @@
     </row>
     <row r="29" spans="1:11" ht="14.4" thickBot="1">
       <c r="A29" s="13" t="e">
-        <f>A28+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B29" s="14" t="s">
@@ -6264,7 +7406,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="7" t="e">
-        <f>A29+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -6300,7 +7442,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="10" t="e">
-        <f>A30+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -6336,7 +7478,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="10" t="e">
-        <f>A31+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -6372,7 +7514,7 @@
     </row>
     <row r="33" spans="1:11" ht="14.4" thickBot="1">
       <c r="A33" s="13" t="e">
-        <f>A32+1</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -6408,7 +7550,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="7" t="e">
-        <f>A33+1</f>
+        <f t="shared" ref="A34:A65" si="1">A33+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -6444,7 +7586,7 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="10" t="e">
-        <f>A34+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -6480,7 +7622,7 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="10" t="e">
-        <f>A35+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -6516,7 +7658,7 @@
     </row>
     <row r="37" spans="1:11" ht="14.4" thickBot="1">
       <c r="A37" s="13" t="e">
-        <f>A36+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -6552,7 +7694,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="7" t="e">
-        <f>A37+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -6588,7 +7730,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="10" t="e">
-        <f>A38+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -6624,7 +7766,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="10" t="e">
-        <f>A39+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -6660,7 +7802,7 @@
     </row>
     <row r="41" spans="1:11" ht="14.4" thickBot="1">
       <c r="A41" s="13" t="e">
-        <f>A40+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -6696,7 +7838,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="7" t="e">
-        <f>A41+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -6732,7 +7874,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="10" t="e">
-        <f>A42+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -6768,7 +7910,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="10" t="e">
-        <f>A43+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -6804,7 +7946,7 @@
     </row>
     <row r="45" spans="1:11" ht="14.4" thickBot="1">
       <c r="A45" s="13" t="e">
-        <f>A44+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B45" s="14" t="s">
@@ -6840,7 +7982,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="7" t="e">
-        <f>A45+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -6876,7 +8018,7 @@
     </row>
     <row r="47" spans="1:11" ht="14.4" thickBot="1">
       <c r="A47" s="13" t="e">
-        <f>A46+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B47" s="14" t="s">
@@ -6912,7 +8054,7 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="7" t="e">
-        <f>A47+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -6948,7 +8090,7 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="10" t="e">
-        <f>A48+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -6984,7 +8126,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="10" t="e">
-        <f>A49+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -7020,7 +8162,7 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="10" t="e">
-        <f>A50+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -7056,7 +8198,7 @@
     </row>
     <row r="52" spans="1:11" ht="14.4" thickBot="1">
       <c r="A52" s="13" t="e">
-        <f>A51+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -7092,7 +8234,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="7" t="e">
-        <f>A52+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -7128,7 +8270,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="10" t="e">
-        <f>A53+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -7164,7 +8306,7 @@
     </row>
     <row r="55" spans="1:11" ht="14.4" thickBot="1">
       <c r="A55" s="13" t="e">
-        <f>A54+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B55" s="14" t="s">
@@ -7200,7 +8342,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="7" t="e">
-        <f>A55+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -7236,7 +8378,7 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="10" t="e">
-        <f>A56+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -7272,7 +8414,7 @@
     </row>
     <row r="58" spans="1:11" ht="14.4" thickBot="1">
       <c r="A58" s="13" t="e">
-        <f>A57+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B58" s="14" t="s">
@@ -7308,7 +8450,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="7" t="e">
-        <f>A58+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -7344,7 +8486,7 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="10" t="e">
-        <f>A59+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -7380,7 +8522,7 @@
     </row>
     <row r="61" spans="1:11" ht="14.4" thickBot="1">
       <c r="A61" s="13" t="e">
-        <f>A60+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B61" s="14" t="s">
@@ -7416,7 +8558,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="7" t="e">
-        <f>A61+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -7452,7 +8594,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="10" t="e">
-        <f>A62+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -7488,7 +8630,7 @@
     </row>
     <row r="64" spans="1:11" ht="14.4" thickBot="1">
       <c r="A64" s="13" t="e">
-        <f>A63+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B64" s="14" t="s">
@@ -7524,7 +8666,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="7" t="e">
-        <f>A64+1</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -7560,7 +8702,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="10" t="e">
-        <f>A65+1</f>
+        <f t="shared" ref="A66:A95" si="2">A65+1</f>
         <v>#VALUE!</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -7596,7 +8738,7 @@
     </row>
     <row r="67" spans="1:11" ht="14.4" thickBot="1">
       <c r="A67" s="13" t="e">
-        <f>A66+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -7632,7 +8774,7 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="7" t="e">
-        <f>A67+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -7668,7 +8810,7 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="10" t="e">
-        <f>A68+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -7704,7 +8846,7 @@
     </row>
     <row r="70" spans="1:11" ht="14.4" thickBot="1">
       <c r="A70" s="13" t="e">
-        <f>A69+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B70" s="14" t="s">
@@ -7740,7 +8882,7 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="7" t="e">
-        <f>A70+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -7776,7 +8918,7 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="10" t="e">
-        <f>A71+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -7812,7 +8954,7 @@
     </row>
     <row r="73" spans="1:11" ht="14.4" thickBot="1">
       <c r="A73" s="13" t="e">
-        <f>A72+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B73" s="14" t="s">
@@ -7848,7 +8990,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="7" t="e">
-        <f>A73+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -7884,7 +9026,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="10" t="e">
-        <f>A74+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -7920,7 +9062,7 @@
     </row>
     <row r="76" spans="1:11" ht="14.4" thickBot="1">
       <c r="A76" s="13" t="e">
-        <f>A75+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B76" s="14" t="s">
@@ -7956,7 +9098,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="7" t="e">
-        <f>A76+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -7992,7 +9134,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="10" t="e">
-        <f>A77+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -8028,7 +9170,7 @@
     </row>
     <row r="79" spans="1:11" ht="14.4" thickBot="1">
       <c r="A79" s="13" t="e">
-        <f>A78+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B79" s="14" t="s">
@@ -8064,7 +9206,7 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="7" t="e">
-        <f>A79+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -8100,7 +9242,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="10" t="e">
-        <f>A80+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -8136,7 +9278,7 @@
     </row>
     <row r="82" spans="1:11" ht="14.4" thickBot="1">
       <c r="A82" s="13" t="e">
-        <f>A81+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B82" s="14" t="s">
@@ -8172,7 +9314,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="7" t="e">
-        <f>A82+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -8208,7 +9350,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="10" t="e">
-        <f>A83+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -8244,7 +9386,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="10" t="e">
-        <f>A84+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -8280,7 +9422,7 @@
     </row>
     <row r="86" spans="1:11" ht="14.4" thickBot="1">
       <c r="A86" s="13" t="e">
-        <f>A85+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B86" s="14" t="s">
@@ -8316,7 +9458,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="7" t="e">
-        <f>A86+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -8352,7 +9494,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="10" t="e">
-        <f>A87+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -8388,7 +9530,7 @@
     </row>
     <row r="89" spans="1:11" ht="14.4" thickBot="1">
       <c r="A89" s="13" t="e">
-        <f>A88+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B89" s="14" t="s">
@@ -8424,7 +9566,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="7" t="e">
-        <f>A89+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -8460,7 +9602,7 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="10" t="e">
-        <f>A90+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -8496,7 +9638,7 @@
     </row>
     <row r="92" spans="1:11" ht="14.4" thickBot="1">
       <c r="A92" s="13" t="e">
-        <f>A91+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B92" s="14" t="s">
@@ -8532,7 +9674,7 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="7" t="e">
-        <f>A92+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -8568,7 +9710,7 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="10" t="e">
-        <f>A93+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -8604,7 +9746,7 @@
     </row>
     <row r="95" spans="1:11" ht="14.4" thickBot="1">
       <c r="A95" s="13" t="e">
-        <f>A94+1</f>
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
       <c r="B95" s="14" t="s">
@@ -8675,7 +9817,7 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="10">
-        <f>A96+1</f>
+        <f t="shared" ref="A97:A139" si="3">A96+1</f>
         <v>2</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -8711,7 +9853,7 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="10">
-        <f>A97+1</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -8747,7 +9889,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="10">
-        <f>A98+1</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -8783,7 +9925,7 @@
     </row>
     <row r="100" spans="1:11" ht="14.4" thickBot="1">
       <c r="A100" s="13">
-        <f>A99+1</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="B100" s="14" t="s">
@@ -8819,7 +9961,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="7">
-        <f>A100+1</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -8855,7 +9997,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="10">
-        <f>A101+1</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -8891,7 +10033,7 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="10">
-        <f>A102+1</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -8927,7 +10069,7 @@
     </row>
     <row r="104" spans="1:11" ht="14.4" thickBot="1">
       <c r="A104" s="13">
-        <f>A103+1</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="B104" s="14" t="s">
@@ -8963,7 +10105,7 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="7">
-        <f>A104+1</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -8999,7 +10141,7 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="10">
-        <f>A105+1</f>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -9035,7 +10177,7 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="10">
-        <f>A106+1</f>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -9071,7 +10213,7 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="10">
-        <f>A107+1</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -9107,7 +10249,7 @@
     </row>
     <row r="109" spans="1:11" ht="14.4" thickBot="1">
       <c r="A109" s="13">
-        <f>A108+1</f>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="B109" s="14" t="s">
@@ -9143,7 +10285,7 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="7">
-        <f>A109+1</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -9179,7 +10321,7 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="10">
-        <f>A110+1</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -9215,7 +10357,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="10">
-        <f>A111+1</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -9251,7 +10393,7 @@
     </row>
     <row r="113" spans="1:11" ht="14.4" thickBot="1">
       <c r="A113" s="13">
-        <f>A112+1</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="B113" s="14" t="s">
@@ -9287,7 +10429,7 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="7">
-        <f>A113+1</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -9323,7 +10465,7 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="10">
-        <f>A114+1</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -9359,7 +10501,7 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="10">
-        <f>A115+1</f>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -9395,7 +10537,7 @@
     </row>
     <row r="117" spans="1:11" ht="14.4" thickBot="1">
       <c r="A117" s="13">
-        <f>A116+1</f>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="B117" s="14" t="s">
@@ -9431,7 +10573,7 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="7">
-        <f>A117+1</f>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -9467,7 +10609,7 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="10">
-        <f>A118+1</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -9503,7 +10645,7 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="10">
-        <f>A119+1</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -9539,7 +10681,7 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="10">
-        <f>A120+1</f>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -9575,7 +10717,7 @@
     </row>
     <row r="122" spans="1:11" ht="14.4" thickBot="1">
       <c r="A122" s="13">
-        <f>A121+1</f>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="B122" s="14" t="s">
@@ -9611,7 +10753,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="7">
-        <f>A122+1</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="B123" s="8" t="s">
@@ -9647,7 +10789,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="10">
-        <f>A123+1</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -9683,7 +10825,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="10">
-        <f>A124+1</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -9719,7 +10861,7 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="10">
-        <f>A125+1</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -9755,7 +10897,7 @@
     </row>
     <row r="127" spans="1:11" ht="14.4" thickBot="1">
       <c r="A127" s="13">
-        <f>A126+1</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="B127" s="14" t="s">
@@ -9791,7 +10933,7 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="7">
-        <f>A127+1</f>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -9827,7 +10969,7 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="10">
-        <f>A128+1</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -9863,7 +11005,7 @@
     </row>
     <row r="130" spans="1:11" ht="14.4" thickBot="1">
       <c r="A130" s="13">
-        <f>A129+1</f>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -9899,7 +11041,7 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="7">
-        <f>A130+1</f>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="B131" s="8" t="s">
@@ -9935,7 +11077,7 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="10">
-        <f>A131+1</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -9971,7 +11113,7 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="10">
-        <f>A132+1</f>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -10007,7 +11149,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="10">
-        <f>A133+1</f>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -10043,7 +11185,7 @@
     </row>
     <row r="135" spans="1:11" ht="14.4" thickBot="1">
       <c r="A135" s="13">
-        <f>A134+1</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="B135" s="14" t="s">
@@ -10079,7 +11221,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="7">
-        <f>A135+1</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="B136" s="8" t="s">
@@ -10115,7 +11257,7 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="10">
-        <f>A136+1</f>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -10151,7 +11293,7 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="10">
-        <f>A137+1</f>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -10187,7 +11329,7 @@
     </row>
     <row r="139" spans="1:11" ht="14.4" thickBot="1">
       <c r="A139" s="13">
-        <f>A138+1</f>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="B139" s="14" t="s">
@@ -10232,4 +11374,917 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="38.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E1" t="s">
+        <v>592</v>
+      </c>
+      <c r="F1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H1" t="s">
+        <v>595</v>
+      </c>
+      <c r="I1" t="s">
+        <v>596</v>
+      </c>
+      <c r="J1" t="s">
+        <v>597</v>
+      </c>
+      <c r="K1" t="s">
+        <v>579</v>
+      </c>
+      <c r="L1" t="s">
+        <v>580</v>
+      </c>
+      <c r="M1" t="s">
+        <v>598</v>
+      </c>
+      <c r="N1" t="s">
+        <v>599</v>
+      </c>
+      <c r="O1" t="s">
+        <v>600</v>
+      </c>
+      <c r="P1" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>602</v>
+      </c>
+      <c r="R1" t="s">
+        <v>603</v>
+      </c>
+      <c r="S1" t="s">
+        <v>604</v>
+      </c>
+      <c r="T1" t="s">
+        <v>605</v>
+      </c>
+      <c r="U1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F2" t="s">
+        <v>593</v>
+      </c>
+      <c r="G2" t="s">
+        <v>594</v>
+      </c>
+      <c r="H2" t="s">
+        <v>595</v>
+      </c>
+      <c r="I2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J2" t="s">
+        <v>597</v>
+      </c>
+      <c r="K2" t="s">
+        <v>579</v>
+      </c>
+      <c r="L2" t="s">
+        <v>580</v>
+      </c>
+      <c r="M2" t="s">
+        <v>598</v>
+      </c>
+      <c r="N2" t="s">
+        <v>599</v>
+      </c>
+      <c r="O2" t="s">
+        <v>600</v>
+      </c>
+      <c r="P2" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>602</v>
+      </c>
+      <c r="R2" t="s">
+        <v>603</v>
+      </c>
+      <c r="S2" t="s">
+        <v>604</v>
+      </c>
+      <c r="T2" t="s">
+        <v>607</v>
+      </c>
+      <c r="U2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E3" t="s">
+        <v>604</v>
+      </c>
+      <c r="F3" t="s">
+        <v>601</v>
+      </c>
+      <c r="G3" t="s">
+        <v>602</v>
+      </c>
+      <c r="H3" t="s">
+        <v>599</v>
+      </c>
+      <c r="I3" t="s">
+        <v>600</v>
+      </c>
+      <c r="J3" t="s">
+        <v>598</v>
+      </c>
+      <c r="K3" t="s">
+        <v>579</v>
+      </c>
+      <c r="L3" t="s">
+        <v>580</v>
+      </c>
+      <c r="M3" t="s">
+        <v>597</v>
+      </c>
+      <c r="N3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O3" t="s">
+        <v>595</v>
+      </c>
+      <c r="P3" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>592</v>
+      </c>
+      <c r="R3" t="s">
+        <v>593</v>
+      </c>
+      <c r="S3" t="s">
+        <v>577</v>
+      </c>
+      <c r="T3" t="s">
+        <v>591</v>
+      </c>
+      <c r="U3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E4" t="s">
+        <v>592</v>
+      </c>
+      <c r="F4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G4" t="s">
+        <v>594</v>
+      </c>
+      <c r="H4" t="s">
+        <v>595</v>
+      </c>
+      <c r="I4" t="s">
+        <v>596</v>
+      </c>
+      <c r="J4" t="s">
+        <v>597</v>
+      </c>
+      <c r="K4" t="s">
+        <v>579</v>
+      </c>
+      <c r="L4" t="s">
+        <v>580</v>
+      </c>
+      <c r="M4" t="s">
+        <v>598</v>
+      </c>
+      <c r="N4" t="s">
+        <v>599</v>
+      </c>
+      <c r="O4" t="s">
+        <v>600</v>
+      </c>
+      <c r="P4" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>602</v>
+      </c>
+      <c r="R4" t="s">
+        <v>603</v>
+      </c>
+      <c r="S4" t="s">
+        <v>604</v>
+      </c>
+      <c r="T4" t="s">
+        <v>607</v>
+      </c>
+      <c r="U4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A5" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C5" t="s">
+        <v>577</v>
+      </c>
+      <c r="D5" t="s">
+        <v>591</v>
+      </c>
+      <c r="E5" t="s">
+        <v>592</v>
+      </c>
+      <c r="F5" t="s">
+        <v>593</v>
+      </c>
+      <c r="G5" t="s">
+        <v>594</v>
+      </c>
+      <c r="H5" t="s">
+        <v>595</v>
+      </c>
+      <c r="I5" t="s">
+        <v>596</v>
+      </c>
+      <c r="J5" t="s">
+        <v>597</v>
+      </c>
+      <c r="K5" t="s">
+        <v>579</v>
+      </c>
+      <c r="L5" t="s">
+        <v>580</v>
+      </c>
+      <c r="M5" t="s">
+        <v>598</v>
+      </c>
+      <c r="N5" t="s">
+        <v>599</v>
+      </c>
+      <c r="O5" t="s">
+        <v>600</v>
+      </c>
+      <c r="P5" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>602</v>
+      </c>
+      <c r="R5" t="s">
+        <v>603</v>
+      </c>
+      <c r="S5" t="s">
+        <v>604</v>
+      </c>
+      <c r="T5" t="s">
+        <v>607</v>
+      </c>
+      <c r="U5" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A6" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C6" t="s">
+        <v>608</v>
+      </c>
+      <c r="D6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E6" t="s">
+        <v>604</v>
+      </c>
+      <c r="F6" t="s">
+        <v>601</v>
+      </c>
+      <c r="G6" t="s">
+        <v>602</v>
+      </c>
+      <c r="H6" t="s">
+        <v>599</v>
+      </c>
+      <c r="I6" t="s">
+        <v>600</v>
+      </c>
+      <c r="J6" t="s">
+        <v>598</v>
+      </c>
+      <c r="K6" t="s">
+        <v>579</v>
+      </c>
+      <c r="L6" t="s">
+        <v>580</v>
+      </c>
+      <c r="M6" t="s">
+        <v>597</v>
+      </c>
+      <c r="N6" t="s">
+        <v>596</v>
+      </c>
+      <c r="O6" t="s">
+        <v>595</v>
+      </c>
+      <c r="P6" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>592</v>
+      </c>
+      <c r="R6" t="s">
+        <v>593</v>
+      </c>
+      <c r="S6" t="s">
+        <v>577</v>
+      </c>
+      <c r="T6" t="s">
+        <v>591</v>
+      </c>
+      <c r="U6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A7" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>607</v>
+      </c>
+      <c r="C7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D7" t="s">
+        <v>603</v>
+      </c>
+      <c r="E7" t="s">
+        <v>604</v>
+      </c>
+      <c r="F7" t="s">
+        <v>601</v>
+      </c>
+      <c r="G7" t="s">
+        <v>602</v>
+      </c>
+      <c r="H7" t="s">
+        <v>599</v>
+      </c>
+      <c r="I7" t="s">
+        <v>600</v>
+      </c>
+      <c r="J7" t="s">
+        <v>598</v>
+      </c>
+      <c r="K7" t="s">
+        <v>579</v>
+      </c>
+      <c r="L7" t="s">
+        <v>580</v>
+      </c>
+      <c r="M7" t="s">
+        <v>597</v>
+      </c>
+      <c r="N7" t="s">
+        <v>596</v>
+      </c>
+      <c r="O7" t="s">
+        <v>595</v>
+      </c>
+      <c r="P7" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>592</v>
+      </c>
+      <c r="R7" t="s">
+        <v>593</v>
+      </c>
+      <c r="S7" t="s">
+        <v>577</v>
+      </c>
+      <c r="T7" t="s">
+        <v>591</v>
+      </c>
+      <c r="U7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A8" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B8" t="s">
+        <v>590</v>
+      </c>
+      <c r="C8" t="s">
+        <v>577</v>
+      </c>
+      <c r="D8" t="s">
+        <v>591</v>
+      </c>
+      <c r="E8" t="s">
+        <v>592</v>
+      </c>
+      <c r="F8" t="s">
+        <v>593</v>
+      </c>
+      <c r="G8" t="s">
+        <v>594</v>
+      </c>
+      <c r="H8" t="s">
+        <v>595</v>
+      </c>
+      <c r="I8" t="s">
+        <v>596</v>
+      </c>
+      <c r="J8" t="s">
+        <v>597</v>
+      </c>
+      <c r="K8" t="s">
+        <v>579</v>
+      </c>
+      <c r="L8" t="s">
+        <v>580</v>
+      </c>
+      <c r="M8" t="s">
+        <v>598</v>
+      </c>
+      <c r="N8" t="s">
+        <v>599</v>
+      </c>
+      <c r="O8" t="s">
+        <v>600</v>
+      </c>
+      <c r="P8" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>602</v>
+      </c>
+      <c r="R8" t="s">
+        <v>603</v>
+      </c>
+      <c r="S8" t="s">
+        <v>604</v>
+      </c>
+      <c r="T8" t="s">
+        <v>605</v>
+      </c>
+      <c r="U8" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="14.4" thickBot="1">
+      <c r="A9" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B9" t="s">
+        <v>607</v>
+      </c>
+      <c r="C9" t="s">
+        <v>608</v>
+      </c>
+      <c r="D9" t="s">
+        <v>603</v>
+      </c>
+      <c r="E9" t="s">
+        <v>604</v>
+      </c>
+      <c r="F9" t="s">
+        <v>601</v>
+      </c>
+      <c r="G9" t="s">
+        <v>602</v>
+      </c>
+      <c r="H9" t="s">
+        <v>599</v>
+      </c>
+      <c r="I9" t="s">
+        <v>600</v>
+      </c>
+      <c r="J9" t="s">
+        <v>598</v>
+      </c>
+      <c r="K9" t="s">
+        <v>579</v>
+      </c>
+      <c r="L9" t="s">
+        <v>580</v>
+      </c>
+      <c r="M9" t="s">
+        <v>597</v>
+      </c>
+      <c r="N9" t="s">
+        <v>596</v>
+      </c>
+      <c r="O9" t="s">
+        <v>595</v>
+      </c>
+      <c r="P9" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>592</v>
+      </c>
+      <c r="R9" t="s">
+        <v>593</v>
+      </c>
+      <c r="S9" t="s">
+        <v>609</v>
+      </c>
+      <c r="T9" t="s">
+        <v>610</v>
+      </c>
+      <c r="U9" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B10" t="s">
+        <v>607</v>
+      </c>
+      <c r="C10" t="s">
+        <v>608</v>
+      </c>
+      <c r="D10" t="s">
+        <v>603</v>
+      </c>
+      <c r="E10" t="s">
+        <v>604</v>
+      </c>
+      <c r="F10" t="s">
+        <v>601</v>
+      </c>
+      <c r="G10" t="s">
+        <v>602</v>
+      </c>
+      <c r="H10" t="s">
+        <v>599</v>
+      </c>
+      <c r="I10" t="s">
+        <v>600</v>
+      </c>
+      <c r="J10" t="s">
+        <v>598</v>
+      </c>
+      <c r="K10" t="s">
+        <v>579</v>
+      </c>
+      <c r="L10" t="s">
+        <v>580</v>
+      </c>
+      <c r="M10" t="s">
+        <v>597</v>
+      </c>
+      <c r="N10" t="s">
+        <v>596</v>
+      </c>
+      <c r="O10" t="s">
+        <v>595</v>
+      </c>
+      <c r="P10" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>592</v>
+      </c>
+      <c r="R10" t="s">
+        <v>593</v>
+      </c>
+      <c r="S10" t="s">
+        <v>577</v>
+      </c>
+      <c r="T10" t="s">
+        <v>591</v>
+      </c>
+      <c r="U10" t="s">
+        <v>609</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:U1">
+    <cfRule type="containsText" dxfId="139" priority="70" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:U1">
+    <cfRule type="containsText" dxfId="137" priority="64" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="136" priority="65" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="135" priority="66" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="134" priority="67" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="133" priority="68" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="132" priority="69" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:U2">
+    <cfRule type="containsText" dxfId="125" priority="63" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:U2">
+    <cfRule type="containsText" dxfId="123" priority="57" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="122" priority="58" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="121" priority="59" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="120" priority="60" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="119" priority="61" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="118" priority="62" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:U3">
+    <cfRule type="containsText" dxfId="111" priority="56" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:U3">
+    <cfRule type="containsText" dxfId="109" priority="50" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="108" priority="51" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="107" priority="52" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="106" priority="53" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="105" priority="54" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="104" priority="55" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:U4">
+    <cfRule type="containsText" dxfId="97" priority="49" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:U4">
+    <cfRule type="containsText" dxfId="95" priority="43" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="94" priority="44" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="93" priority="45" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="92" priority="46" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="91" priority="47" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="90" priority="48" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:U5">
+    <cfRule type="containsText" dxfId="83" priority="42" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:U5">
+    <cfRule type="containsText" dxfId="81" priority="36" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="80" priority="37" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="79" priority="38" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="78" priority="39" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="77" priority="40" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="76" priority="41" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:U6">
+    <cfRule type="containsText" dxfId="69" priority="35" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:U6">
+    <cfRule type="containsText" dxfId="67" priority="29" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="66" priority="30" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="65" priority="31" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="64" priority="32" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="63" priority="33" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="62" priority="34" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:U7">
+    <cfRule type="containsText" dxfId="55" priority="28" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:U7">
+    <cfRule type="containsText" dxfId="53" priority="22" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="23" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="51" priority="24" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="50" priority="25" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="26" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="27" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:U8">
+    <cfRule type="containsText" dxfId="41" priority="21" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:U8">
+    <cfRule type="containsText" dxfId="39" priority="15" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="16" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="17" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="18" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="35" priority="19" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="20" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:U9">
+    <cfRule type="containsText" dxfId="27" priority="14" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:U9">
+    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="10" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="12" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:U10">
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="dcd">
+      <formula>NOT(ISERROR(SEARCH("dcd",A10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:U10">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="alkaline phosphatase">
+      <formula>NOT(ISERROR(SEARCH("alkaline phosphatase",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="rsxA">
+      <formula>NOT(ISERROR(SEARCH("rsxA",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="cell wall hydrolase">
+      <formula>NOT(ISERROR(SEARCH("cell wall hydrolase",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="DUF3465">
+      <formula>NOT(ISERROR(SEARCH("DUF3465",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="terB">
+      <formula>NOT(ISERROR(SEARCH("terB",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="metG">
+      <formula>NOT(ISERROR(SEARCH("metG",A10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>